--- a/data/availability/projects/madinet-masr/talala.xlsx
+++ b/data/availability/projects/madinet-masr/talala.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1059,7 +1059,6 @@
       <c r="G2" t="n">
         <v>65</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1092,7 +1091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1116,7 +1115,6 @@
       <c r="G3" t="n">
         <v>105</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1149,7 +1147,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1173,7 +1171,6 @@
       <c r="G4" t="n">
         <v>135</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1352,7 +1349,6 @@
       <c r="G7" t="n">
         <v>216</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1470,7 +1466,6 @@
       <c r="G9" t="n">
         <v>240</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1588,7 +1583,6 @@
       <c r="G11" t="n">
         <v>179</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1645,7 +1639,6 @@
       <c r="G12" t="n">
         <v>208</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1702,7 +1695,6 @@
       <c r="G13" t="n">
         <v>247</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1759,7 +1751,6 @@
       <c r="G14" t="n">
         <v>288</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/madinet-masr/talala.xlsx
+++ b/data/availability/projects/madinet-masr/talala.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
